--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 11:24</t>
+    <t xml:space="preserve">2026-09-09 19:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:02</t>
+    <t xml:space="preserve">2026-09-17 04:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:19</t>
+    <t xml:space="preserve">2026-09-25 11:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:13</t>
+    <t xml:space="preserve">2026-09-26 23:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2020_nuble.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Reg_Mujeres</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:47</t>
+    <t xml:space="preserve">2026-10-05 04:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Nuble</t>
+    <t xml:space="preserve">Region de Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
